--- a/reports/jobs_2026-10-18.xlsx
+++ b/reports/jobs_2026-10-18.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Mumbai 1 available jobs Ok</t>
+          <t>Mumbai 0 available jobs Ok</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mumbai 1 available jobs Ok</t>
+          <t>Mumbai 0 available jobs Ok</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Mumbai 1 available jobs</t>
+          <t>Mumbai 0 available jobs</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Mumbai 1 available jobs Ok</t>
+          <t>Mumbai 0 available jobs Ok</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mumbai 1 available jobs Ok</t>
+          <t>Mumbai 0 available jobs Ok</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5524,35 +5524,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INDmoney</t>
+          <t>Log9 Materials</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.indmoney.com/careers</t>
+          <t>https://www.log9materials.com/careers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.indmoney.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Log9 Materials</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://www.log9materials.com/careers</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5561,18 +5541,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5581,18 +5561,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5601,18 +5581,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Blinkit</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://blinkit.com/careers</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5621,6 +5601,26 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CRED</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://careers.cred.club/</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://careers.cred.club/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -5644,35 +5644,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CRED</t>
+          <t>Cleartrip</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://careers.cred.club/</t>
+          <t>https://www.cleartrip.com/careers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://careers.cred.club/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Cleartrip</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://www.cleartrip.com/careers</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5681,18 +5661,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -5701,18 +5681,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5721,18 +5701,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5741,18 +5721,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Netcore Cloud</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://netcorecloud.com/careers/</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5761,38 +5741,38 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FirstCry</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.firstcry.com/careers</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OYO</t>
+          <t>Zomato</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.oyorooms.com/careers/</t>
+          <t>https://www.zomato.com/careers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.oyorooms.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Zomato</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>https://www.zomato.com/careers</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -5801,18 +5781,58 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ninjacart</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://ninjacart.com/careers/</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://ninjacart.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Tata 1mg</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.1mg.com/jobs</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.1mg.com/jobs", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Swiggy</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>https://careers.swiggy.com/</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5821,18 +5841,18 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -5841,18 +5861,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -5861,18 +5881,18 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5881,6 +5901,26 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Zoom India</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://careers.zoom.us/</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: net::ERR_CONNECTION_RESET at https://careers.zoom.us/
+Call log:
+  - navigating to "https://careers.zoom.us/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
